--- a/artfynd/A 44802-2026 artfynd.xlsx
+++ b/artfynd/A 44802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137247965</v>
       </c>
       <c r="B2" t="n">
-        <v>89230</v>
+        <v>89234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137247972</v>
       </c>
       <c r="B3" t="n">
-        <v>89332</v>
+        <v>89336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137247974</v>
       </c>
       <c r="B4" t="n">
-        <v>89334</v>
+        <v>89338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137247968</v>
       </c>
       <c r="B6" t="n">
-        <v>89310</v>
+        <v>89314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
